--- a/excel/trendings.xlsx
+++ b/excel/trendings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +588,82 @@
         <v>27.47</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>38</v>
+      </c>
+      <c r="C10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>74</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
